--- a/exports/trend_1d/TRENT_full_report.xlsx
+++ b/exports/trend_1d/TRENT_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q81"/>
+  <dimension ref="A1:U81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>10.89</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42111</v>
+        <v>42114</v>
       </c>
       <c r="H2" t="n">
-        <v>92.40000000000001</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="I2" t="n">
         <v>91.49718434797299</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="K2" t="n">
-        <v>-2.43</v>
+        <v>-7.18</v>
       </c>
       <c r="L2" t="n">
-        <v>4.22</v>
+        <v>8.34</v>
       </c>
       <c r="M2" t="n">
         <v>1.99</v>
       </c>
       <c r="N2" t="n">
-        <v>2.42</v>
+        <v>4.87</v>
       </c>
       <c r="O2" t="n">
         <v>1.83</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>4</v>
+      </c>
+      <c r="U2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>11.56</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42143</v>
+        <v>42144</v>
       </c>
       <c r="H3" t="n">
-        <v>79.40000000000001</v>
+        <v>86.7</v>
       </c>
       <c r="I3" t="n">
         <v>86.31378378189392</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K3" t="n">
-        <v>9.67</v>
+        <v>1.37</v>
       </c>
       <c r="L3" t="n">
         <v>5.01</v>
@@ -612,7 +647,7 @@
         <v>1.06</v>
       </c>
       <c r="N3" t="n">
-        <v>3.84</v>
+        <v>9.19</v>
       </c>
       <c r="O3" t="n">
         <v>-4.87</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42124</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>15.74</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42159</v>
+        <v>42160</v>
       </c>
       <c r="H4" t="n">
-        <v>77.09999999999999</v>
+        <v>75.7</v>
       </c>
       <c r="I4" t="n">
         <v>75.78579057621826</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K4" t="n">
-        <v>-11.07</v>
+        <v>-12.69</v>
       </c>
       <c r="L4" t="n">
         <v>15.8</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42152</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -705,22 +764,22 @@
         <v>15.89</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42223</v>
+        <v>42226</v>
       </c>
       <c r="H5" t="n">
-        <v>81.59999999999999</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="I5" t="n">
         <v>83.18511790060792</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="K5" t="n">
-        <v>-7.79</v>
+        <v>-14.8</v>
       </c>
       <c r="L5" t="n">
-        <v>12.42</v>
+        <v>18.36</v>
       </c>
       <c r="M5" t="n">
         <v>2.53</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42180</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -762,22 +833,22 @@
         <v>13.26</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42256</v>
+        <v>42257</v>
       </c>
       <c r="H6" t="n">
-        <v>79.59999999999999</v>
+        <v>77.8</v>
       </c>
       <c r="I6" t="n">
         <v>78.69704577791994</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K6" t="n">
-        <v>-8.4</v>
+        <v>-10.47</v>
       </c>
       <c r="L6" t="n">
-        <v>10.24</v>
+        <v>10.93</v>
       </c>
       <c r="M6" t="n">
         <v>3.44</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42243</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>10.58</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42269</v>
+        <v>42270</v>
       </c>
       <c r="H7" t="n">
-        <v>83.90000000000001</v>
+        <v>86.2</v>
       </c>
       <c r="I7" t="n">
         <v>86.0295873311336</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K7" t="n">
-        <v>-7.84</v>
+        <v>-10.8</v>
       </c>
       <c r="L7" t="n">
         <v>13.5</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42271</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>13.74</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42398</v>
+        <v>42401</v>
       </c>
       <c r="H8" t="n">
-        <v>103.9</v>
+        <v>103.4</v>
       </c>
       <c r="I8" t="n">
         <v>103.4247396066112</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="K8" t="n">
-        <v>20.53</v>
+        <v>19.95</v>
       </c>
       <c r="L8" t="n">
         <v>4.06</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>86</v>
+        <v>87</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42271</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>6</v>
+      </c>
+      <c r="U8" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>11.06</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42461</v>
+        <v>42464</v>
       </c>
       <c r="H9" t="n">
-        <v>106.6</v>
+        <v>106.7</v>
       </c>
       <c r="I9" t="n">
         <v>106.6371835639375</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K9" t="n">
-        <v>-3.09</v>
+        <v>-3.19</v>
       </c>
       <c r="L9" t="n">
         <v>8.32</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42425</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>11.49</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42520</v>
+        <v>42521</v>
       </c>
       <c r="H10" t="n">
-        <v>116.1</v>
+        <v>109</v>
       </c>
       <c r="I10" t="n">
         <v>111.3821200444271</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K10" t="n">
-        <v>8.81</v>
+        <v>2.16</v>
       </c>
       <c r="L10" t="n">
         <v>2.25</v>
@@ -1011,7 +1130,7 @@
         <v>1.67</v>
       </c>
       <c r="N10" t="n">
-        <v>2.76</v>
+        <v>6.12</v>
       </c>
       <c r="O10" t="n">
         <v>0.09</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42488</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1047,22 +1178,22 @@
         <v>15.69</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42550</v>
+        <v>42551</v>
       </c>
       <c r="H11" t="n">
-        <v>119.5</v>
+        <v>121.1</v>
       </c>
       <c r="I11" t="n">
         <v>119.5759897485666</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K11" t="n">
-        <v>-9.630000000000001</v>
+        <v>-11.1</v>
       </c>
       <c r="L11" t="n">
-        <v>12.57</v>
+        <v>12.84</v>
       </c>
       <c r="M11" t="n">
         <v>2.04</v>
@@ -1077,7 +1208,19 @@
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42551</v>
+      </c>
+      <c r="S11" t="b">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>10.04</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42633</v>
+        <v>42634</v>
       </c>
       <c r="H12" t="n">
-        <v>146.3</v>
+        <v>143.2</v>
       </c>
       <c r="I12" t="n">
         <v>144.7410918450647</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K12" t="n">
-        <v>20.81</v>
+        <v>18.25</v>
       </c>
       <c r="L12" t="n">
         <v>4.62</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42579</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3</v>
+      </c>
+      <c r="U12" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>14.59</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42711</v>
+        <v>42712</v>
       </c>
       <c r="H13" t="n">
-        <v>132.1</v>
+        <v>135.8</v>
       </c>
       <c r="I13" t="n">
         <v>133.4574603493846</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K13" t="n">
-        <v>7.75</v>
+        <v>5.17</v>
       </c>
       <c r="L13" t="n">
         <v>6.15</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42642</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>4</v>
+      </c>
+      <c r="U13" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>13.7</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>42873</v>
+        <v>42874</v>
       </c>
       <c r="H14" t="n">
-        <v>165.1</v>
+        <v>162.6</v>
       </c>
       <c r="I14" t="n">
         <v>164.4293386768017</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="K14" t="n">
-        <v>21.58</v>
+        <v>19.73</v>
       </c>
       <c r="L14" t="n">
         <v>6.33</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>110</v>
+        <v>111</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>42733</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>6</v>
+      </c>
+      <c r="U14" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="15">
@@ -1275,28 +1454,28 @@
         <v>8.880000000000001</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>42929</v>
+        <v>42930</v>
       </c>
       <c r="H15" t="n">
-        <v>165.8</v>
+        <v>174.8</v>
       </c>
       <c r="I15" t="n">
         <v>168.9014890276324</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.97</v>
+        <v>-7.5</v>
       </c>
       <c r="L15" t="n">
-        <v>10.09</v>
+        <v>11.5</v>
       </c>
       <c r="M15" t="n">
         <v>8.09</v>
       </c>
       <c r="N15" t="n">
-        <v>3.42</v>
+        <v>5.43</v>
       </c>
       <c r="O15" t="n">
         <v>-1.51</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>42880</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>14.02</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>43129</v>
+        <v>43130</v>
       </c>
       <c r="H16" t="n">
-        <v>216.3</v>
+        <v>210</v>
       </c>
       <c r="I16" t="n">
         <v>213.7524292320426</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K16" t="n">
-        <v>23.74</v>
+        <v>20.14</v>
       </c>
       <c r="L16" t="n">
         <v>7.21</v>
@@ -1362,7 +1553,19 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>135</v>
+        <v>136</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>42943</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>8</v>
+      </c>
+      <c r="U16" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="17">
@@ -1389,22 +1592,22 @@
         <v>9.59</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>43171</v>
+        <v>43172</v>
       </c>
       <c r="H17" t="n">
-        <v>222.4</v>
+        <v>233.1</v>
       </c>
       <c r="I17" t="n">
         <v>223.7955623222492</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K17" t="n">
-        <v>-5.9</v>
+        <v>-11</v>
       </c>
       <c r="L17" t="n">
-        <v>9.48</v>
+        <v>13</v>
       </c>
       <c r="M17" t="n">
         <v>2.39</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>43153</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,22 +1661,22 @@
         <v>13.61</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>43252</v>
+        <v>43255</v>
       </c>
       <c r="H18" t="n">
-        <v>218.6</v>
+        <v>214.7</v>
       </c>
       <c r="I18" t="n">
         <v>217.5978617860459</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="K18" t="n">
-        <v>-6.22</v>
+        <v>-7.89</v>
       </c>
       <c r="L18" t="n">
-        <v>7.85</v>
+        <v>8.41</v>
       </c>
       <c r="M18" t="n">
         <v>0.93</v>
@@ -1476,7 +1691,19 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>43187</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>4</v>
+      </c>
+      <c r="U18" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -1503,28 +1730,28 @@
         <v>8.75</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>43290</v>
+        <v>43291</v>
       </c>
       <c r="H19" t="n">
-        <v>213.9</v>
+        <v>227.1</v>
       </c>
       <c r="I19" t="n">
         <v>219.4252523693804</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K19" t="n">
-        <v>0.37</v>
+        <v>-5.78</v>
       </c>
       <c r="L19" t="n">
-        <v>3.07</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="M19" t="n">
-        <v>0.8</v>
+        <v>1.12</v>
       </c>
       <c r="N19" t="n">
-        <v>4.23</v>
+        <v>6.17</v>
       </c>
       <c r="O19" t="n">
         <v>-1.78</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>43279</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>11.35</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43370</v>
+        <v>43371</v>
       </c>
       <c r="H20" t="n">
-        <v>229.4</v>
+        <v>222.2</v>
       </c>
       <c r="I20" t="n">
         <v>225.648859271749</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K20" t="n">
-        <v>1.01</v>
+        <v>-2.16</v>
       </c>
       <c r="L20" t="n">
         <v>7</v>
@@ -1581,7 +1820,7 @@
         <v>2.3</v>
       </c>
       <c r="N20" t="n">
-        <v>2.71</v>
+        <v>3.14</v>
       </c>
       <c r="O20" t="n">
         <v>6.17</v>
@@ -1590,7 +1829,19 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43307</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>4</v>
+      </c>
+      <c r="U20" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -1617,22 +1868,22 @@
         <v>14.87</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43446</v>
+        <v>43447</v>
       </c>
       <c r="H21" t="n">
-        <v>226.6</v>
+        <v>233.2</v>
       </c>
       <c r="I21" t="n">
         <v>231.7126510004734</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.98</v>
+        <v>-4.95</v>
       </c>
       <c r="L21" t="n">
-        <v>6.62</v>
+        <v>10.13</v>
       </c>
       <c r="M21" t="n">
         <v>2.59</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43398</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -1674,28 +1937,28 @@
         <v>10.02</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43510</v>
+        <v>43511</v>
       </c>
       <c r="H22" t="n">
-        <v>228.3</v>
+        <v>222.1</v>
       </c>
       <c r="I22" t="n">
         <v>224.9152538937421</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K22" t="n">
-        <v>-2.1</v>
+        <v>-4.76</v>
       </c>
       <c r="L22" t="n">
-        <v>4.33</v>
+        <v>4.8</v>
       </c>
       <c r="M22" t="n">
         <v>1.46</v>
       </c>
       <c r="N22" t="n">
-        <v>2.11</v>
+        <v>2.72</v>
       </c>
       <c r="O22" t="n">
         <v>2.91</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43461</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1731,28 +2006,28 @@
         <v>9.56</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43535</v>
+        <v>43536</v>
       </c>
       <c r="H23" t="n">
-        <v>226.7</v>
+        <v>239.9</v>
       </c>
       <c r="I23" t="n">
         <v>232.6463982759745</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K23" t="n">
-        <v>-2.07</v>
+        <v>-8.01</v>
       </c>
       <c r="L23" t="n">
-        <v>5.67</v>
+        <v>9.19</v>
       </c>
       <c r="M23" t="n">
         <v>1.3</v>
       </c>
       <c r="N23" t="n">
-        <v>3.55</v>
+        <v>5.82</v>
       </c>
       <c r="O23" t="n">
         <v>-2.72</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43524</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>12.64</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43670</v>
+        <v>43671</v>
       </c>
       <c r="H24" t="n">
-        <v>276.8</v>
+        <v>273</v>
       </c>
       <c r="I24" t="n">
         <v>275.1825572216467</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="K24" t="n">
-        <v>15.38</v>
+        <v>13.8</v>
       </c>
       <c r="L24" t="n">
         <v>5.88</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>91</v>
+        <v>92</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43552</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>5</v>
+      </c>
+      <c r="U24" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>11.64</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43685</v>
+        <v>43686</v>
       </c>
       <c r="H25" t="n">
-        <v>289.2</v>
+        <v>298</v>
       </c>
       <c r="I25" t="n">
         <v>297.8343941311838</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K25" t="n">
-        <v>-5.93</v>
+        <v>-9.16</v>
       </c>
       <c r="L25" t="n">
         <v>10.88</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43706</v>
+      </c>
+      <c r="S25" t="b">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>12.95</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43789</v>
+        <v>43790</v>
       </c>
       <c r="H26" t="n">
-        <v>331.2</v>
+        <v>328.6</v>
       </c>
       <c r="I26" t="n">
         <v>330.7035760310089</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K26" t="n">
-        <v>11.14</v>
+        <v>10.27</v>
       </c>
       <c r="L26" t="n">
         <v>3.36</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43706</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>4</v>
+      </c>
+      <c r="U26" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="27">
@@ -1959,28 +2282,28 @@
         <v>11.98</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43825</v>
+        <v>43826</v>
       </c>
       <c r="H27" t="n">
-        <v>349.9</v>
+        <v>363.6</v>
       </c>
       <c r="I27" t="n">
         <v>360.1710074822795</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K27" t="n">
-        <v>-6.48</v>
+        <v>-10.65</v>
       </c>
       <c r="L27" t="n">
-        <v>9.220000000000001</v>
+        <v>11.08</v>
       </c>
       <c r="M27" t="n">
         <v>1.44</v>
       </c>
       <c r="N27" t="n">
-        <v>2.27</v>
+        <v>3.92</v>
       </c>
       <c r="O27" t="n">
         <v>-0.79</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43797</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>3</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>10.82</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>43896</v>
+        <v>43899</v>
       </c>
       <c r="H28" t="n">
-        <v>462.5</v>
+        <v>440.2</v>
       </c>
       <c r="I28" t="n">
         <v>448.1287448227379</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="K28" t="n">
-        <v>27.2</v>
+        <v>21.07</v>
       </c>
       <c r="L28" t="n">
         <v>4.4</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>43860</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>19.14</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>43980</v>
+        <v>43983</v>
       </c>
       <c r="H29" t="n">
-        <v>312.6</v>
+        <v>338.6</v>
       </c>
       <c r="I29" t="n">
         <v>321.8970832661628</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="K29" t="n">
-        <v>28.99</v>
+        <v>23.08</v>
       </c>
       <c r="L29" t="n">
         <v>5.7</v>
@@ -2103,7 +2450,19 @@
         <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>43916</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>4</v>
+      </c>
+      <c r="U29" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>16.71</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>44036</v>
+        <v>44039</v>
       </c>
       <c r="H30" t="n">
-        <v>385</v>
+        <v>366.8</v>
       </c>
       <c r="I30" t="n">
         <v>383.1570880050109</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="K30" t="n">
-        <v>13.7</v>
+        <v>8.33</v>
       </c>
       <c r="L30" t="n">
         <v>5.49</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>44007</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,22 +2558,22 @@
         <v>15.46</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>44064</v>
+        <v>44067</v>
       </c>
       <c r="H31" t="n">
-        <v>404</v>
+        <v>415.2</v>
       </c>
       <c r="I31" t="n">
         <v>412.898761639847</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K31" t="n">
-        <v>-10.14</v>
+        <v>-13.2</v>
       </c>
       <c r="L31" t="n">
-        <v>14.23</v>
+        <v>21.05</v>
       </c>
       <c r="M31" t="n">
         <v>0.97</v>
@@ -2217,7 +2588,19 @@
         <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>44042</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>11.8</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>44095</v>
+        <v>44096</v>
       </c>
       <c r="H32" t="n">
-        <v>432.8</v>
+        <v>422.9</v>
       </c>
       <c r="I32" t="n">
         <v>432.5214683962467</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K32" t="n">
-        <v>4.24</v>
+        <v>1.85</v>
       </c>
       <c r="L32" t="n">
         <v>2.7</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>44070</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>17.77</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>44146</v>
+        <v>44147</v>
       </c>
       <c r="H33" t="n">
-        <v>468.6</v>
+        <v>484</v>
       </c>
       <c r="I33" t="n">
         <v>481.9279007271384</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K33" t="n">
-        <v>-10.81</v>
+        <v>-14.45</v>
       </c>
       <c r="L33" t="n">
         <v>22.94</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>44098</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>3</v>
+      </c>
+      <c r="U33" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>17.72</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>44209</v>
+        <v>44210</v>
       </c>
       <c r="H34" t="n">
-        <v>448.8</v>
+        <v>436.4</v>
       </c>
       <c r="I34" t="n">
         <v>446.843084418772</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K34" t="n">
-        <v>-7.27</v>
+        <v>-9.83</v>
       </c>
       <c r="L34" t="n">
         <v>12.62</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>44161</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>3</v>
+      </c>
+      <c r="U34" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -2415,28 +2834,28 @@
         <v>10.91</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>44242</v>
+        <v>44243</v>
       </c>
       <c r="H35" t="n">
-        <v>467.8</v>
+        <v>500.2</v>
       </c>
       <c r="I35" t="n">
         <v>474.5267260110077</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K35" t="n">
-        <v>-7.2</v>
+        <v>-14.62</v>
       </c>
       <c r="L35" t="n">
-        <v>8.91</v>
+        <v>15.79</v>
       </c>
       <c r="M35" t="n">
         <v>1.43</v>
       </c>
       <c r="N35" t="n">
-        <v>3.84</v>
+        <v>6.93</v>
       </c>
       <c r="O35" t="n">
         <v>-2.76</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>44224</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>14.05</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>44278</v>
+        <v>44279</v>
       </c>
       <c r="H36" t="n">
-        <v>542.5</v>
+        <v>523.4</v>
       </c>
       <c r="I36" t="n">
         <v>530.5772322794066</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K36" t="n">
-        <v>8.460000000000001</v>
+        <v>4.64</v>
       </c>
       <c r="L36" t="n">
         <v>5.38</v>
@@ -2502,7 +2933,19 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>44252</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>19.81</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>44333</v>
+        <v>44334</v>
       </c>
       <c r="H37" t="n">
-        <v>530.1</v>
+        <v>552.2</v>
       </c>
       <c r="I37" t="n">
         <v>536.6455103252028</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K37" t="n">
-        <v>-1.28</v>
+        <v>-5.5</v>
       </c>
       <c r="L37" t="n">
         <v>7.76</v>
@@ -2550,7 +2993,7 @@
         <v>1.92</v>
       </c>
       <c r="N37" t="n">
-        <v>3.05</v>
+        <v>4.17</v>
       </c>
       <c r="O37" t="n">
         <v>-3.52</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>44280</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>3</v>
+      </c>
+      <c r="U37" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>13.41</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>44491</v>
+        <v>44494</v>
       </c>
       <c r="H38" t="n">
-        <v>700.6</v>
+        <v>680.4</v>
       </c>
       <c r="I38" t="n">
         <v>680.53455392611</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="K38" t="n">
-        <v>26.87</v>
+        <v>23.22</v>
       </c>
       <c r="L38" t="n">
         <v>3.51</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>110</v>
+        <v>111</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>44343</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>6</v>
+      </c>
+      <c r="U38" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="39">
@@ -2643,22 +3110,22 @@
         <v>18.9</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>44515</v>
+        <v>44516</v>
       </c>
       <c r="H39" t="n">
-        <v>771.5</v>
+        <v>793.6</v>
       </c>
       <c r="I39" t="n">
         <v>774.2564614023646</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K39" t="n">
-        <v>-13.39</v>
+        <v>-16.64</v>
       </c>
       <c r="L39" t="n">
-        <v>14.93</v>
+        <v>17.84</v>
       </c>
       <c r="M39" t="n">
         <v>5.74</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>44497</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,22 +3179,22 @@
         <v>12.5</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>44526</v>
+        <v>44529</v>
       </c>
       <c r="H40" t="n">
-        <v>694.4</v>
+        <v>684.5</v>
       </c>
       <c r="I40" t="n">
         <v>694.3717415708376</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K40" t="n">
-        <v>-12.5</v>
+        <v>-13.75</v>
       </c>
       <c r="L40" t="n">
-        <v>13.9</v>
+        <v>16.63</v>
       </c>
       <c r="M40" t="n">
         <v>2.22</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>44525</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,22 +3248,22 @@
         <v>13.06</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>44572</v>
+        <v>44573</v>
       </c>
       <c r="H41" t="n">
-        <v>746.1</v>
+        <v>763.5</v>
       </c>
       <c r="I41" t="n">
         <v>752.3042939195836</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K41" t="n">
-        <v>-9</v>
+        <v>-11.54</v>
       </c>
       <c r="L41" t="n">
-        <v>9.470000000000001</v>
+        <v>12.05</v>
       </c>
       <c r="M41" t="n">
         <v>1.78</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>44560</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,28 +3317,28 @@
         <v>10.53</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>44586</v>
+        <v>44588</v>
       </c>
       <c r="H42" t="n">
-        <v>719.6</v>
+        <v>682</v>
       </c>
       <c r="I42" t="n">
         <v>710.8952383906177</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K42" t="n">
-        <v>-5.75</v>
+        <v>-10.67</v>
       </c>
       <c r="L42" t="n">
-        <v>8.279999999999999</v>
+        <v>12.56</v>
       </c>
       <c r="M42" t="n">
         <v>2.67</v>
       </c>
       <c r="N42" t="n">
-        <v>5.06</v>
+        <v>5.23</v>
       </c>
       <c r="O42" t="n">
         <v>2.33</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S42" t="b">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -2871,28 +3386,28 @@
         <v>18.34</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>44628</v>
+        <v>44629</v>
       </c>
       <c r="H43" t="n">
-        <v>718.7</v>
+        <v>762.5</v>
       </c>
       <c r="I43" t="n">
         <v>760.9073426854361</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K43" t="n">
-        <v>-5.38</v>
+        <v>-11.8</v>
       </c>
       <c r="L43" t="n">
-        <v>11.01</v>
+        <v>12.9</v>
       </c>
       <c r="M43" t="n">
         <v>3.85</v>
       </c>
       <c r="N43" t="n">
-        <v>4.85</v>
+        <v>6.09</v>
       </c>
       <c r="O43" t="n">
         <v>-5.23</v>
@@ -2901,7 +3416,19 @@
         <v>1</v>
       </c>
       <c r="Q43" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>16.12</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>44686</v>
+        <v>44687</v>
       </c>
       <c r="H44" t="n">
-        <v>808.2</v>
+        <v>764.5</v>
       </c>
       <c r="I44" t="n">
         <v>795.8728793733483</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K44" t="n">
-        <v>5.99</v>
+        <v>0.26</v>
       </c>
       <c r="L44" t="n">
         <v>6.44</v>
@@ -2949,7 +3476,7 @@
         <v>3.11</v>
       </c>
       <c r="N44" t="n">
-        <v>4.28</v>
+        <v>5.41</v>
       </c>
       <c r="O44" t="n">
         <v>6.09</v>
@@ -2958,7 +3485,19 @@
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>3</v>
+      </c>
+      <c r="U44" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>13.5</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>44747</v>
+        <v>44748</v>
       </c>
       <c r="H45" t="n">
-        <v>746.9</v>
+        <v>781.3</v>
       </c>
       <c r="I45" t="n">
         <v>759.5714021840157</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="K45" t="n">
-        <v>2.3</v>
+        <v>-2.2</v>
       </c>
       <c r="L45" t="n">
         <v>4.62</v>
@@ -3015,7 +3554,19 @@
         <v>1</v>
       </c>
       <c r="Q45" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>3</v>
+      </c>
+      <c r="U45" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>13.16</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>44792</v>
+        <v>44795</v>
       </c>
       <c r="H46" t="n">
-        <v>932.1</v>
+        <v>876.1</v>
       </c>
       <c r="I46" t="n">
         <v>898.2624532785181</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="K46" t="n">
-        <v>19.3</v>
+        <v>12.13</v>
       </c>
       <c r="L46" t="n">
         <v>5.03</v>
@@ -3063,7 +3614,7 @@
         <v>0.51</v>
       </c>
       <c r="N46" t="n">
-        <v>3.94</v>
+        <v>6.01</v>
       </c>
       <c r="O46" t="n">
         <v>4.61</v>
@@ -3072,7 +3623,19 @@
         <v>1</v>
       </c>
       <c r="Q46" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -3099,28 +3662,28 @@
         <v>16.55</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>44862</v>
+        <v>44865</v>
       </c>
       <c r="H47" t="n">
-        <v>972.6</v>
+        <v>1018.6</v>
       </c>
       <c r="I47" t="n">
         <v>997.9163215599602</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="K47" t="n">
-        <v>-11.01</v>
+        <v>-16.27</v>
       </c>
       <c r="L47" t="n">
-        <v>14.04</v>
+        <v>17.42</v>
       </c>
       <c r="M47" t="n">
         <v>2.17</v>
       </c>
       <c r="N47" t="n">
-        <v>4.3</v>
+        <v>4.73</v>
       </c>
       <c r="O47" t="n">
         <v>-6.01</v>
@@ -3129,7 +3692,19 @@
         <v>1</v>
       </c>
       <c r="Q47" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>4</v>
+      </c>
+      <c r="U47" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="48">
@@ -3156,22 +3731,22 @@
         <v>10.16</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>44880</v>
+        <v>44881</v>
       </c>
       <c r="H48" t="n">
-        <v>944.1</v>
+        <v>929.9</v>
       </c>
       <c r="I48" t="n">
         <v>943.7027806547208</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K48" t="n">
-        <v>-7.31</v>
+        <v>-8.710000000000001</v>
       </c>
       <c r="L48" t="n">
-        <v>8.699999999999999</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="M48" t="n">
         <v>1.26</v>
@@ -3186,7 +3761,19 @@
         <v>1</v>
       </c>
       <c r="Q48" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S48" t="b">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3213,28 +3800,28 @@
         <v>10.98</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>44965</v>
+        <v>44966</v>
       </c>
       <c r="H49" t="n">
-        <v>824</v>
+        <v>894.6</v>
       </c>
       <c r="I49" t="n">
         <v>850.5943928776229</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K49" t="n">
-        <v>11.39</v>
+        <v>3.8</v>
       </c>
       <c r="L49" t="n">
         <v>6.68</v>
       </c>
       <c r="M49" t="n">
-        <v>0.68</v>
+        <v>4.37</v>
       </c>
       <c r="N49" t="n">
-        <v>5.69</v>
+        <v>8.57</v>
       </c>
       <c r="O49" t="n">
         <v>-1.5</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>4</v>
+      </c>
+      <c r="U49" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>12.56</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45119</v>
+        <v>45120</v>
       </c>
       <c r="H50" t="n">
-        <v>1125.3</v>
+        <v>1110.7</v>
       </c>
       <c r="I50" t="n">
         <v>1112.082231583072</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="K50" t="n">
-        <v>25.79</v>
+        <v>24.16</v>
       </c>
       <c r="L50" t="n">
         <v>5.8</v>
@@ -3300,7 +3899,19 @@
         <v>1</v>
       </c>
       <c r="Q50" t="n">
-        <v>103</v>
+        <v>104</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>6</v>
+      </c>
+      <c r="U50" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="51">
@@ -3327,28 +3938,28 @@
         <v>8.300000000000001</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45147</v>
+        <v>45148</v>
       </c>
       <c r="H51" t="n">
-        <v>1191.9</v>
+        <v>1263.6</v>
       </c>
       <c r="I51" t="n">
         <v>1195.224936445665</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K51" t="n">
-        <v>-7.31</v>
+        <v>-13.77</v>
       </c>
       <c r="L51" t="n">
-        <v>8.43</v>
+        <v>14.95</v>
       </c>
       <c r="M51" t="n">
-        <v>0.68</v>
+        <v>1.24</v>
       </c>
       <c r="N51" t="n">
-        <v>4.32</v>
+        <v>6.02</v>
       </c>
       <c r="O51" t="n">
         <v>-1.3</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>10.51</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45219</v>
+        <v>45222</v>
       </c>
       <c r="H52" t="n">
-        <v>1357.4</v>
+        <v>1328</v>
       </c>
       <c r="I52" t="n">
         <v>1330.114571373552</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="K52" t="n">
-        <v>7.42</v>
+        <v>5.1</v>
       </c>
       <c r="L52" t="n">
         <v>5.56</v>
@@ -3414,7 +4037,19 @@
         <v>1</v>
       </c>
       <c r="Q52" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>3</v>
+      </c>
+      <c r="U52" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="53">
@@ -3441,22 +4076,22 @@
         <v>8.48</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45229</v>
+        <v>45230</v>
       </c>
       <c r="H53" t="n">
-        <v>1413.2</v>
+        <v>1436.5</v>
       </c>
       <c r="I53" t="n">
         <v>1424.268168438683</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K53" t="n">
-        <v>-6.42</v>
+        <v>-8.17</v>
       </c>
       <c r="L53" t="n">
-        <v>7.59</v>
+        <v>8.68</v>
       </c>
       <c r="M53" t="n">
         <v>1</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>8.789999999999999</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45324</v>
+        <v>45327</v>
       </c>
       <c r="H54" t="n">
-        <v>2084</v>
+        <v>2018.1</v>
       </c>
       <c r="I54" t="n">
         <v>2025.122756758466</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="K54" t="n">
-        <v>45.07</v>
+        <v>40.49</v>
       </c>
       <c r="L54" t="n">
         <v>1.66</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>4</v>
+      </c>
+      <c r="U54" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="55">
@@ -3555,28 +4214,28 @@
         <v>12.22</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45328</v>
+        <v>45329</v>
       </c>
       <c r="H55" t="n">
-        <v>2023.3</v>
+        <v>2405</v>
       </c>
       <c r="I55" t="n">
         <v>2249.848739875524</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K55" t="n">
-        <v>-0.26</v>
+        <v>-19.17</v>
       </c>
       <c r="L55" t="n">
-        <v>5.05</v>
+        <v>20.07</v>
       </c>
       <c r="M55" t="n">
         <v>1.57</v>
       </c>
       <c r="N55" t="n">
-        <v>0.26</v>
+        <v>18.87</v>
       </c>
       <c r="O55" t="n">
         <v>-3.16</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S55" t="b">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>1</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>21.89</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45489</v>
+        <v>45491</v>
       </c>
       <c r="H56" t="n">
-        <v>3764.9</v>
+        <v>3539</v>
       </c>
       <c r="I56" t="n">
         <v>3539.317252116126</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="K56" t="n">
-        <v>56.54</v>
+        <v>47.15</v>
       </c>
       <c r="L56" t="n">
         <v>18.09</v>
@@ -3633,7 +4304,7 @@
         <v>2.56</v>
       </c>
       <c r="N56" t="n">
-        <v>3.26</v>
+        <v>6</v>
       </c>
       <c r="O56" t="n">
         <v>18.87</v>
@@ -3642,7 +4313,19 @@
         <v>1</v>
       </c>
       <c r="Q56" t="n">
-        <v>109</v>
+        <v>110</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>6</v>
+      </c>
+      <c r="U56" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="57">
@@ -3669,28 +4352,28 @@
         <v>11.67</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45503</v>
+        <v>45504</v>
       </c>
       <c r="H57" t="n">
-        <v>3747</v>
+        <v>3892.7</v>
       </c>
       <c r="I57" t="n">
         <v>3754.912650886609</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K57" t="n">
-        <v>-5.88</v>
+        <v>-9.99</v>
       </c>
       <c r="L57" t="n">
-        <v>6.63</v>
+        <v>11.51</v>
       </c>
       <c r="M57" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="N57" t="n">
-        <v>2.3</v>
+        <v>3.89</v>
       </c>
       <c r="O57" t="n">
         <v>-6</v>
@@ -3699,7 +4382,19 @@
         <v>1</v>
       </c>
       <c r="Q57" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,22 +4421,22 @@
         <v>10.04</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="H58" t="n">
-        <v>3564.6</v>
+        <v>3480.5</v>
       </c>
       <c r="I58" t="n">
         <v>3526.436435999137</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K58" t="n">
-        <v>-8.43</v>
+        <v>-10.59</v>
       </c>
       <c r="L58" t="n">
-        <v>10.5</v>
+        <v>11.04</v>
       </c>
       <c r="M58" t="n">
         <v>3.22</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S58" t="b">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>1</v>
+      </c>
+      <c r="U58" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -3783,28 +4490,28 @@
         <v>13.85</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45512</v>
+        <v>45513</v>
       </c>
       <c r="H59" t="n">
-        <v>3762.7</v>
+        <v>4183.6</v>
       </c>
       <c r="I59" t="n">
         <v>3962.688238156629</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K59" t="n">
-        <v>-8.109999999999999</v>
+        <v>-20.2</v>
       </c>
       <c r="L59" t="n">
-        <v>9.710000000000001</v>
+        <v>22.09</v>
       </c>
       <c r="M59" t="n">
-        <v>1.31</v>
+        <v>1.68</v>
       </c>
       <c r="N59" t="n">
-        <v>4.82</v>
+        <v>11.19</v>
       </c>
       <c r="O59" t="n">
         <v>-2.36</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S59" t="b">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>1</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>17.25</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45588</v>
+        <v>45589</v>
       </c>
       <c r="H60" t="n">
-        <v>5007.5</v>
+        <v>4992</v>
       </c>
       <c r="I60" t="n">
         <v>4996.714558842581</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K60" t="n">
-        <v>19.69</v>
+        <v>19.32</v>
       </c>
       <c r="L60" t="n">
         <v>10.34</v>
@@ -3870,7 +4589,19 @@
         <v>1</v>
       </c>
       <c r="Q60" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>3</v>
+      </c>
+      <c r="U60" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>9.890000000000001</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45658</v>
+        <v>45659</v>
       </c>
       <c r="H61" t="n">
-        <v>4712</v>
+        <v>4880.7</v>
       </c>
       <c r="I61" t="n">
         <v>4787.980555030958</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K61" t="n">
-        <v>5.61</v>
+        <v>2.23</v>
       </c>
       <c r="L61" t="n">
         <v>2.04</v>
@@ -3918,7 +4649,7 @@
         <v>2.2</v>
       </c>
       <c r="N61" t="n">
-        <v>2.98</v>
+        <v>3.58</v>
       </c>
       <c r="O61" t="n">
         <v>-0.31</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>4</v>
+      </c>
+      <c r="U61" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="62">
@@ -3954,25 +4697,25 @@
         <v>10.6</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45664</v>
+        <v>45665</v>
       </c>
       <c r="H62" t="n">
-        <v>4582.9</v>
+        <v>4466.1</v>
       </c>
       <c r="I62" t="n">
         <v>4491.254494430676</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K62" t="n">
-        <v>-6.1</v>
+        <v>-8.49</v>
       </c>
       <c r="L62" t="n">
-        <v>6.59</v>
+        <v>9.98</v>
       </c>
       <c r="M62" t="n">
-        <v>-0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="N62" t="n">
         <v>4.23</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S62" t="b">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>1</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -4011,19 +4766,19 @@
         <v>11.29</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45688</v>
+        <v>45689</v>
       </c>
       <c r="H63" t="n">
-        <v>3835.5</v>
+        <v>4126.3</v>
       </c>
       <c r="I63" t="n">
         <v>4102.621660752785</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K63" t="n">
-        <v>14.12</v>
+        <v>7.61</v>
       </c>
       <c r="L63" t="n">
         <v>2.6</v>
@@ -4032,7 +4787,7 @@
         <v>1.69</v>
       </c>
       <c r="N63" t="n">
-        <v>4.39</v>
+        <v>7.58</v>
       </c>
       <c r="O63" t="n">
         <v>-2.55</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4068,28 +4835,28 @@
         <v>16.92</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45693</v>
+        <v>45694</v>
       </c>
       <c r="H64" t="n">
-        <v>3833.3</v>
+        <v>3518.1</v>
       </c>
       <c r="I64" t="n">
         <v>3551.182686542088</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K64" t="n">
-        <v>-7.1</v>
+        <v>-14.74</v>
       </c>
       <c r="L64" t="n">
-        <v>8.66</v>
+        <v>15.26</v>
       </c>
       <c r="M64" t="n">
         <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>6.27</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="O64" t="n">
         <v>7.58</v>
@@ -4098,7 +4865,19 @@
         <v>1</v>
       </c>
       <c r="Q64" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S64" t="b">
+        <v>0</v>
+      </c>
+      <c r="T64" t="n">
+        <v>1</v>
+      </c>
+      <c r="U64" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -4125,19 +4904,19 @@
         <v>23.04</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>45744</v>
+        <v>45748</v>
       </c>
       <c r="H65" t="n">
-        <v>3550.1</v>
+        <v>3717.8</v>
       </c>
       <c r="I65" t="n">
         <v>3618.109492307539</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="K65" t="n">
-        <v>-0.91</v>
+        <v>-5.68</v>
       </c>
       <c r="L65" t="n">
         <v>10.76</v>
@@ -4146,7 +4925,7 @@
         <v>1.65</v>
       </c>
       <c r="N65" t="n">
-        <v>4.08</v>
+        <v>4.72</v>
       </c>
       <c r="O65" t="n">
         <v>-8.220000000000001</v>
@@ -4155,7 +4934,19 @@
         <v>1</v>
       </c>
       <c r="Q65" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>3</v>
+      </c>
+      <c r="U65" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="66">
@@ -4182,28 +4973,28 @@
         <v>12.39</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>45751</v>
+        <v>45754</v>
       </c>
       <c r="H66" t="n">
-        <v>3708.6</v>
+        <v>3160.6</v>
       </c>
       <c r="I66" t="n">
         <v>3407.268352096276</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K66" t="n">
-        <v>-0.25</v>
+        <v>-14.99</v>
       </c>
       <c r="L66" t="n">
-        <v>4.35</v>
+        <v>19.52</v>
       </c>
       <c r="M66" t="n">
-        <v>0.92</v>
+        <v>10</v>
       </c>
       <c r="N66" t="n">
-        <v>1.98</v>
+        <v>14.78</v>
       </c>
       <c r="O66" t="n">
         <v>4.72</v>
@@ -4212,7 +5003,19 @@
         <v>1</v>
       </c>
       <c r="Q66" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S66" t="b">
+        <v>0</v>
+      </c>
+      <c r="T66" t="n">
+        <v>1</v>
+      </c>
+      <c r="U66" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -4239,22 +5042,22 @@
         <v>17.49</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>45791</v>
+        <v>45792</v>
       </c>
       <c r="H67" t="n">
-        <v>3574.7</v>
+        <v>3718.3</v>
       </c>
       <c r="I67" t="n">
         <v>3651.067324189634</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K67" t="n">
-        <v>-13.1</v>
+        <v>-17.65</v>
       </c>
       <c r="L67" t="n">
-        <v>16.22</v>
+        <v>18.75</v>
       </c>
       <c r="M67" t="n">
         <v>4.24</v>
@@ -4269,7 +5072,19 @@
         <v>1</v>
       </c>
       <c r="Q67" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -4296,28 +5111,28 @@
         <v>13.37</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>45841</v>
+        <v>45842</v>
       </c>
       <c r="H68" t="n">
-        <v>4127.3</v>
+        <v>3637.3</v>
       </c>
       <c r="I68" t="n">
         <v>3796.82285681431</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K68" t="n">
-        <v>11</v>
+        <v>-2.18</v>
       </c>
       <c r="L68" t="n">
         <v>5.24</v>
       </c>
       <c r="M68" t="n">
-        <v>2.17</v>
+        <v>8.33</v>
       </c>
       <c r="N68" t="n">
-        <v>2.58</v>
+        <v>11.87</v>
       </c>
       <c r="O68" t="n">
         <v>4.02</v>
@@ -4326,7 +5141,19 @@
         <v>1</v>
       </c>
       <c r="Q68" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>3</v>
+      </c>
+      <c r="U68" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="69">
@@ -4353,19 +5180,19 @@
         <v>15</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>45877</v>
+        <v>45880</v>
       </c>
       <c r="H69" t="n">
-        <v>3544.7</v>
+        <v>3629</v>
       </c>
       <c r="I69" t="n">
         <v>3595.407546236686</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K69" t="n">
-        <v>2.55</v>
+        <v>0.23</v>
       </c>
       <c r="L69" t="n">
         <v>6.03</v>
@@ -4383,7 +5210,19 @@
         <v>1</v>
       </c>
       <c r="Q69" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>2</v>
+      </c>
+      <c r="U69" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -4410,22 +5249,22 @@
         <v>9.039999999999999</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>45910</v>
+        <v>45911</v>
       </c>
       <c r="H70" t="n">
-        <v>3462</v>
+        <v>3447.3</v>
       </c>
       <c r="I70" t="n">
         <v>3454.526301297858</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K70" t="n">
-        <v>-4.6</v>
+        <v>-5.01</v>
       </c>
       <c r="L70" t="n">
-        <v>5.01</v>
+        <v>5.39</v>
       </c>
       <c r="M70" t="n">
         <v>0.06</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>2</v>
+      </c>
+      <c r="U70" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -4467,19 +5318,19 @@
         <v>7.92</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="H71" t="n">
-        <v>2792.9</v>
+        <v>2859.7</v>
       </c>
       <c r="I71" t="n">
         <v>2849.070697036828</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K71" t="n">
-        <v>18.98</v>
+        <v>17.05</v>
       </c>
       <c r="L71" t="n">
         <v>1.49</v>
@@ -4497,7 +5348,19 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>71</v>
+        <v>72</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>4</v>
+      </c>
+      <c r="U71" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="72">
@@ -4524,28 +5387,28 @@
         <v>7.3</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="H72" t="n">
-        <v>2953.2</v>
+        <v>2698.4</v>
       </c>
       <c r="I72" t="n">
         <v>2754.39297334311</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K72" t="n">
-        <v>3.27</v>
+        <v>-5.64</v>
       </c>
       <c r="L72" t="n">
-        <v>2.48</v>
+        <v>6.89</v>
       </c>
       <c r="M72" t="n">
-        <v>-0</v>
+        <v>5</v>
       </c>
       <c r="N72" t="n">
-        <v>1.39</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="O72" t="n">
         <v>2.39</v>
@@ -4554,7 +5417,19 @@
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S72" t="b">
+        <v>1</v>
+      </c>
+      <c r="T72" t="n">
+        <v>2</v>
+      </c>
+      <c r="U72" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -4581,19 +5456,19 @@
         <v>10.68</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="H73" t="n">
-        <v>2548.5</v>
+        <v>2675.1</v>
       </c>
       <c r="I73" t="n">
         <v>2668.453666799612</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K73" t="n">
-        <v>5.56</v>
+        <v>0.86</v>
       </c>
       <c r="L73" t="n">
         <v>3.97</v>
@@ -4602,7 +5477,7 @@
         <v>4.81</v>
       </c>
       <c r="N73" t="n">
-        <v>2.74</v>
+        <v>4.97</v>
       </c>
       <c r="O73" t="n">
         <v>-8.630000000000001</v>
@@ -4611,7 +5486,19 @@
         <v>1</v>
       </c>
       <c r="Q73" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S73" t="b">
+        <v>1</v>
+      </c>
+      <c r="T73" t="n">
+        <v>2</v>
+      </c>
+      <c r="U73" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -4638,19 +5525,19 @@
         <v>11.42</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>46078</v>
+        <v>46079</v>
       </c>
       <c r="H74" t="n">
-        <v>2614.7</v>
+        <v>2570.7</v>
       </c>
       <c r="I74" t="n">
         <v>2591.567497121566</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K74" t="n">
-        <v>-2.26</v>
+        <v>-3.9</v>
       </c>
       <c r="L74" t="n">
         <v>5.17</v>
@@ -4668,7 +5555,19 @@
         <v>1</v>
       </c>
       <c r="Q74" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S74" t="b">
+        <v>1</v>
+      </c>
+      <c r="T74" t="n">
+        <v>2</v>
+      </c>
+      <c r="U74" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="75">
@@ -4695,19 +5594,19 @@
         <v>9.449999999999999</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="H75" t="n">
-        <v>2367.1</v>
+        <v>2555.7</v>
       </c>
       <c r="I75" t="n">
         <v>2481.895757379168</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="K75" t="n">
-        <v>7.92</v>
+        <v>0.58</v>
       </c>
       <c r="L75" t="n">
         <v>2.35</v>
@@ -4716,7 +5615,7 @@
         <v>4.59</v>
       </c>
       <c r="N75" t="n">
-        <v>7</v>
+        <v>7.97</v>
       </c>
       <c r="O75" t="n">
         <v>-1.68</v>
@@ -4725,7 +5624,19 @@
         <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R75" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S75" t="b">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>2</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -4752,28 +5663,28 @@
         <v>14.82</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="H76" t="n">
-        <v>3343.8</v>
+        <v>2927.8</v>
       </c>
       <c r="I76" t="n">
         <v>3100.253878845342</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K76" t="n">
-        <v>30.84</v>
+        <v>14.56</v>
       </c>
       <c r="L76" t="n">
         <v>5.18</v>
       </c>
       <c r="M76" t="n">
-        <v>2.45</v>
+        <v>7.89</v>
       </c>
       <c r="N76" t="n">
-        <v>4.13</v>
+        <v>12.44</v>
       </c>
       <c r="O76" t="n">
         <v>7.97</v>
@@ -4782,7 +5693,19 @@
         <v>1</v>
       </c>
       <c r="Q76" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R76" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S76" t="b">
+        <v>1</v>
+      </c>
+      <c r="T76" t="n">
+        <v>4</v>
+      </c>
+      <c r="U76" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="77">
@@ -4809,22 +5732,22 @@
         <v>14.41</v>
       </c>
       <c r="G77" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="H77" t="n">
-        <v>3050</v>
+        <v>3107.7</v>
       </c>
       <c r="I77" t="n">
         <v>3092.139472249941</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K77" t="n">
-        <v>-4.17</v>
+        <v>-6.14</v>
       </c>
       <c r="L77" t="n">
-        <v>5.2</v>
+        <v>6.26</v>
       </c>
       <c r="M77" t="n">
         <v>1.03</v>
@@ -4839,7 +5762,19 @@
         <v>1</v>
       </c>
       <c r="Q77" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R77" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S77" t="b">
+        <v>1</v>
+      </c>
+      <c r="T77" t="n">
+        <v>2</v>
+      </c>
+      <c r="U77" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="78">
@@ -4866,22 +5801,22 @@
         <v>7.45</v>
       </c>
       <c r="G78" s="1" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="H78" t="n">
-        <v>2924</v>
+        <v>2905</v>
       </c>
       <c r="I78" t="n">
         <v>2913.548761749493</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K78" t="n">
-        <v>-5.91</v>
+        <v>-6.52</v>
       </c>
       <c r="L78" t="n">
-        <v>6.23</v>
+        <v>6.93</v>
       </c>
       <c r="M78" t="n">
         <v>1.41</v>
@@ -4896,7 +5831,19 @@
         <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R78" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S78" t="b">
+        <v>0</v>
+      </c>
+      <c r="T78" t="n">
+        <v>1</v>
+      </c>
+      <c r="U78" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -4923,28 +5870,28 @@
         <v>6.51</v>
       </c>
       <c r="G79" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="H79" t="n">
-        <v>2580</v>
+        <v>2906</v>
       </c>
       <c r="I79" t="n">
         <v>2765.903285709565</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K79" t="n">
-        <v>11.19</v>
+        <v>-0.03</v>
       </c>
       <c r="L79" t="n">
         <v>1.71</v>
       </c>
       <c r="M79" t="n">
-        <v>1.19</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="N79" t="n">
-        <v>1.45</v>
+        <v>12.64</v>
       </c>
       <c r="O79" t="n">
         <v>-0.65</v>
@@ -4953,7 +5900,19 @@
         <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R79" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S79" t="b">
+        <v>1</v>
+      </c>
+      <c r="T79" t="n">
+        <v>3</v>
+      </c>
+      <c r="U79" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="80">
@@ -4980,22 +5939,22 @@
         <v>10.87</v>
       </c>
       <c r="G80" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="H80" t="n">
-        <v>2775.8</v>
+        <v>2727.5</v>
       </c>
       <c r="I80" t="n">
         <v>2744.328121440301</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K80" t="n">
-        <v>-4.48</v>
+        <v>-6.14</v>
       </c>
       <c r="L80" t="n">
-        <v>5.23</v>
+        <v>7.91</v>
       </c>
       <c r="M80" t="n">
         <v>0.74</v>
@@ -5010,7 +5969,19 @@
         <v>1</v>
       </c>
       <c r="Q80" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R80" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S80" t="b">
+        <v>0</v>
+      </c>
+      <c r="T80" t="n">
+        <v>1</v>
+      </c>
+      <c r="U80" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="81">
@@ -5061,6 +6032,14 @@
       <c r="Q81" t="n">
         <v>4</v>
       </c>
+      <c r="R81" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S81" t="b">
+        <v>1</v>
+      </c>
+      <c r="T81" t="inlineStr"/>
+      <c r="U81" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10019,7 +10998,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>52.9</v>
+        <v>54.4</v>
       </c>
     </row>
     <row r="6">
@@ -10029,7 +11008,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7">
@@ -10039,7 +11018,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="8">
@@ -10049,7 +11028,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -10059,7 +11038,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="10">
@@ -10069,7 +11048,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="11">
@@ -10079,7 +11058,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12">
@@ -10089,7 +11068,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="13">
@@ -10099,7 +11078,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>38</v>
+        <v>35.4</v>
       </c>
     </row>
     <row r="14">
@@ -10109,7 +11088,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.61</v>
+        <v>-1.03</v>
       </c>
     </row>
     <row r="15">
@@ -10119,7 +11098,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8.15</v>
+        <v>4.01</v>
       </c>
     </row>
     <row r="16">
@@ -10129,7 +11108,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-1.04</v>
+        <v>-6.2</v>
       </c>
     </row>
     <row r="17">
@@ -10139,7 +11118,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>56.54</v>
+        <v>47.15</v>
       </c>
     </row>
     <row r="18">
@@ -10149,7 +11128,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>45.6</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -10159,7 +11138,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>7.45</v>
+        <v>9.23</v>
       </c>
     </row>
     <row r="20">
@@ -10169,7 +11148,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>6.33</v>
+        <v>7.91</v>
       </c>
     </row>
     <row r="21">
@@ -10189,7 +11168,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
     </row>
     <row r="23">
@@ -10199,7 +11178,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
     </row>
     <row r="24">
@@ -10209,7 +11188,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.08</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="25">
@@ -10219,7 +11198,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>8.09</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26">
@@ -10229,7 +11208,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4.35</v>
+        <v>5.89</v>
       </c>
     </row>
     <row r="27">
@@ -10239,7 +11218,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>12.14</v>
+        <v>18.87</v>
       </c>
     </row>
     <row r="28">
@@ -10249,7 +11228,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>44</v>
+        <v>59</v>
       </c>
     </row>
     <row r="29">
